--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N73_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N73_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.4541508310843</v>
+        <v>4.9487995100512</v>
       </c>
       <c r="D2" t="n">
-        <v>23.64393127461024</v>
+        <v>3.842138832124163</v>
       </c>
       <c r="E2" t="n">
-        <v>14.88944663715747</v>
+        <v>2.419535078538089</v>
       </c>
       <c r="F2" t="n">
-        <v>18.51615477671455</v>
+        <v>3.008875151216114</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.23304410539925</v>
+        <v>9.787869667127378</v>
       </c>
       <c r="D3" t="n">
-        <v>60.67624082803933</v>
+        <v>9.859889134556392</v>
       </c>
       <c r="E3" t="n">
-        <v>14.88944663715747</v>
+        <v>2.419535078538089</v>
       </c>
       <c r="F3" t="n">
-        <v>18.51615477671455</v>
+        <v>3.008875151216114</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
